--- a/data/planningevents.xlsx
+++ b/data/planningevents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10737\Desktop\Planning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouyan\课程资料\2026春航天任务分析与设计\航天任务课程实验资料汇总\大作业3\Planning\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B80354-DE22-4840-87AF-7F01C57770CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120B91AA-99D7-499E-A07E-2A40E0951BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -379,9 +379,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -398,7 +398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -416,7 +416,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -434,7 +434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -453,7 +453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -471,7 +471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -489,7 +489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -507,7 +507,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -525,7 +525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -543,7 +543,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -561,7 +561,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>

--- a/data/planningevents.xlsx
+++ b/data/planningevents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouyan\课程资料\2026春航天任务分析与设计\航天任务课程实验资料汇总\大作业3\Planning\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120B91AA-99D7-499E-A07E-2A40E0951BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDA00BC-FFFF-41FD-965A-DCCE8CF78A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,6 +380,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
